--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -706,22 +706,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -738,22 +741,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -875,22 +881,25 @@
         <v>41</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>17.07</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.8</v>
       </c>
       <c r="J12">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1739,22 +1748,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1771,22 +1783,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1908,22 +1923,25 @@
         <v>41</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>17.07</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.8</v>
       </c>
       <c r="J12">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -54,7 +54,7 @@
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
@@ -63,6 +62,15 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>QUÍMICA II</t>
+  </si>
+  <si>
+    <t>INTRODUCCIÓN A LA BIOQUÍMICA</t>
+  </si>
+  <si>
     <t>2AEV</t>
   </si>
   <si>
@@ -103,12 +111,6 @@
   </si>
   <si>
     <t>6ALCV</t>
-  </si>
-  <si>
-    <t>QUÍMICA II</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN A LA BIOQUÍMICA</t>
   </si>
 </sst>
 </file>
@@ -472,11 +474,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -522,10 +524,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -537,10 +539,10 @@
         <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>64.52</v>
+        <v>64.5</v>
       </c>
       <c r="H2" s="1">
-        <v>35.48</v>
+        <v>35.5</v>
       </c>
       <c r="I2" s="2">
         <v>6.6</v>
@@ -560,25 +562,25 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>19</v>
       </c>
       <c r="G3" s="1">
-        <v>54.76</v>
+        <v>53.7</v>
       </c>
       <c r="H3" s="1">
-        <v>45.24</v>
+        <v>46.3</v>
       </c>
       <c r="I3" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -592,10 +594,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -607,10 +609,10 @@
         <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>83.33</v>
+        <v>83.3</v>
       </c>
       <c r="H4" s="1">
-        <v>16.67</v>
+        <v>16.7</v>
       </c>
       <c r="I4" s="2">
         <v>7.2</v>
@@ -627,10 +629,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>32</v>
@@ -662,10 +664,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>33</v>
@@ -677,10 +679,10 @@
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>90.91</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="I6" s="2">
         <v>6.9</v>
@@ -694,31 +696,25 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
-        <v>94.12</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>5.88</v>
+        <v>25.1</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -732,28 +728,28 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>90.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>9.300000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -767,28 +763,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D9">
+        <v>43</v>
+      </c>
+      <c r="E9">
         <v>39</v>
       </c>
-      <c r="E9">
-        <v>34</v>
-      </c>
       <c r="F9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>87.18000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H9" s="1">
-        <v>12.82</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -802,25 +798,25 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>87.5</v>
+        <v>87.2</v>
       </c>
       <c r="H10" s="1">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="I10" s="2">
         <v>7.7</v>
@@ -837,28 +833,28 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>89.19</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>10.81</v>
+        <v>12.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -872,28 +868,28 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>82.93000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="H12" s="1">
-        <v>17.07</v>
+        <v>10.8</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -904,31 +900,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I13" s="2">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -939,31 +935,25 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>235</v>
+      </c>
+      <c r="E14">
+        <v>208</v>
+      </c>
+      <c r="F14">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14">
-        <v>32</v>
-      </c>
-      <c r="E14">
-        <v>32</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="I14" s="2">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -974,36 +964,193 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <v>34</v>
+      </c>
+      <c r="E15">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>32</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>66</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
         <v>26</v>
       </c>
-      <c r="E15">
+      <c r="E18">
         <v>20</v>
       </c>
-      <c r="F15">
+      <c r="F18">
         <v>6</v>
       </c>
-      <c r="G15" s="1">
-        <v>76.92</v>
-      </c>
-      <c r="H15" s="1">
-        <v>23.08</v>
-      </c>
-      <c r="I15" s="2">
+      <c r="G18" s="1">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="I18" s="2">
         <v>6.4</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>26</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H19" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>494</v>
+      </c>
+      <c r="E20">
+        <v>419</v>
+      </c>
+      <c r="F20">
+        <v>75</v>
+      </c>
+      <c r="G20" s="1">
+        <v>84.8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1014,11 +1161,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1064,31 +1211,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>35.5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1099,28 +1249,31 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>53.7</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>46.3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1128,31 +1281,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1160,31 +1316,34 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1192,63 +1351,63 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>9.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>25.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1256,31 +1415,34 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>5.9</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1288,31 +1450,34 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D9">
+        <v>43</v>
+      </c>
+      <c r="E9">
         <v>39</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
       <c r="F9">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1320,31 +1485,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>87.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>12.8</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1352,31 +1520,34 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1384,668 +1555,289 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>10.8</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.9</v>
       </c>
       <c r="J13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>235</v>
+      </c>
+      <c r="E14">
+        <v>208</v>
+      </c>
+      <c r="F14">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14">
-        <v>32</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>32</v>
-      </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>11.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.7</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <v>34</v>
+      </c>
+      <c r="E15">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>32</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>66</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
         <v>26</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19">
         <v>26</v>
       </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
-      <c r="J15">
-        <v>26</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="G19" s="1">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H19" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1">
-        <v>64.52</v>
-      </c>
-      <c r="H2" s="1">
-        <v>35.48</v>
-      </c>
-      <c r="I2" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>42</v>
-      </c>
-      <c r="E3">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1">
-        <v>54.76</v>
-      </c>
-      <c r="H3" s="1">
-        <v>45.24</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1">
-        <v>83.33</v>
-      </c>
-      <c r="H4" s="1">
-        <v>16.67</v>
-      </c>
-      <c r="I4" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5">
-        <v>32</v>
-      </c>
-      <c r="E5">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H5" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="D20">
+        <v>494</v>
+      </c>
+      <c r="E20">
+        <v>419</v>
+      </c>
+      <c r="F20">
+        <v>75</v>
+      </c>
+      <c r="G20" s="1">
+        <v>84.8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="I20" s="2">
         <v>7.6</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1">
-        <v>90.91</v>
-      </c>
-      <c r="H6" s="1">
-        <v>9.09</v>
-      </c>
-      <c r="I6" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>32</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>94.12</v>
-      </c>
-      <c r="H7" s="1">
-        <v>5.88</v>
-      </c>
-      <c r="I7" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>39</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1">
-        <v>90.7</v>
-      </c>
-      <c r="H8" s="1">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I8" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>34</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1">
-        <v>87.18000000000001</v>
-      </c>
-      <c r="H9" s="1">
-        <v>12.82</v>
-      </c>
-      <c r="I9" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>35</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H10" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>37</v>
-      </c>
-      <c r="E11">
-        <v>33</v>
-      </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
-      <c r="G11" s="1">
-        <v>89.19</v>
-      </c>
-      <c r="H11" s="1">
-        <v>10.81</v>
-      </c>
-      <c r="I11" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12">
-        <v>41</v>
-      </c>
-      <c r="E12">
-        <v>34</v>
-      </c>
-      <c r="F12">
-        <v>7</v>
-      </c>
-      <c r="G12" s="1">
-        <v>82.93000000000001</v>
-      </c>
-      <c r="H12" s="1">
-        <v>17.07</v>
-      </c>
-      <c r="I12" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13">
-        <v>34</v>
-      </c>
-      <c r="E13">
-        <v>34</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>100</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14">
-        <v>32</v>
-      </c>
-      <c r="E14">
-        <v>32</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>100</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>9.4</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15">
-        <v>26</v>
-      </c>
-      <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="F15">
-        <v>6</v>
-      </c>
-      <c r="G15" s="1">
-        <v>76.92</v>
-      </c>
-      <c r="H15" s="1">
-        <v>23.08</v>
-      </c>
-      <c r="I15" s="2">
-        <v>6.4</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="33">
   <si>
     <t>Docente</t>
   </si>
@@ -62,13 +62,16 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>QUÍMICA II</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>INTRODUCCIÓN A LA BIOQUÍMICA</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>2AEV</t>
@@ -478,7 +481,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -524,10 +527,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -559,10 +562,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -594,10 +597,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -629,10 +632,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>32</v>
@@ -664,10 +667,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>33</v>
@@ -698,6 +701,9 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
       <c r="D7">
         <v>167</v>
       </c>
@@ -728,10 +734,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>34</v>
@@ -763,10 +769,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>43</v>
@@ -798,10 +804,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>39</v>
@@ -833,10 +839,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>40</v>
@@ -868,10 +874,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>37</v>
@@ -903,10 +909,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>42</v>
@@ -937,6 +943,9 @@
       <c r="A14" t="s">
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
       <c r="D14">
         <v>235</v>
       </c>
@@ -970,7 +979,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>34</v>
@@ -1005,7 +1014,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>32</v>
@@ -1036,6 +1045,9 @@
       <c r="A17" t="s">
         <v>13</v>
       </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
       <c r="D17">
         <v>66</v>
       </c>
@@ -1069,7 +1081,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18">
         <v>26</v>
@@ -1100,6 +1112,9 @@
       <c r="A19" t="s">
         <v>14</v>
       </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
       <c r="D19">
         <v>26</v>
       </c>
@@ -1126,8 +1141,8 @@
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>15</v>
+      <c r="B20" t="s">
+        <v>18</v>
       </c>
       <c r="D20">
         <v>494</v>
@@ -1211,10 +1226,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -1246,10 +1261,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -1281,10 +1296,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -1316,10 +1331,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>32</v>
@@ -1351,10 +1366,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>33</v>
@@ -1385,6 +1400,9 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
       <c r="D7">
         <v>167</v>
       </c>
@@ -1415,10 +1433,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>34</v>
@@ -1450,10 +1468,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>43</v>
@@ -1485,10 +1503,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>39</v>
@@ -1520,10 +1538,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>40</v>
@@ -1555,10 +1573,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>37</v>
@@ -1590,10 +1608,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>42</v>
@@ -1624,6 +1642,9 @@
       <c r="A14" t="s">
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
       <c r="D14">
         <v>235</v>
       </c>
@@ -1657,7 +1678,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>34</v>
@@ -1692,7 +1713,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>32</v>
@@ -1723,6 +1744,9 @@
       <c r="A17" t="s">
         <v>13</v>
       </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
       <c r="D17">
         <v>66</v>
       </c>
@@ -1756,7 +1780,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18">
         <v>26</v>
@@ -1787,6 +1811,9 @@
       <c r="A19" t="s">
         <v>14</v>
       </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
       <c r="D19">
         <v>26</v>
       </c>
@@ -1813,8 +1840,8 @@
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>15</v>
+      <c r="B20" t="s">
+        <v>18</v>
       </c>
       <c r="D20">
         <v>494</v>

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="33">
   <si>
     <t>Docente</t>
   </si>
@@ -1235,6 +1236,705 @@
         <v>31</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>41</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>41</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>32</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>33</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>33</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>167</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>167</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>167</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>34</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>43</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>43</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>39</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>39</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>39</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>40</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>37</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>37</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>37</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>42</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>42</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>235</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>235</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>235</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>34</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>34</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>34</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>32</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>32</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>66</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>66</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>26</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>26</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19">
+        <v>26</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>26</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>26</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>494</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>494</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>494</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>31</v>
+      </c>
+      <c r="E2">
         <v>20</v>
       </c>
       <c r="F2">

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -639,28 +639,28 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>28</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H5" s="1">
-        <v>12.5</v>
+        <v>15.2</v>
       </c>
       <c r="I5" s="2">
         <v>7.6</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -706,28 +706,28 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E7">
         <v>125</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1">
-        <v>74.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="I7" s="2">
         <v>6.9</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1146,28 +1146,28 @@
         <v>18</v>
       </c>
       <c r="D20">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E20">
         <v>419</v>
       </c>
       <c r="F20">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" s="1">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="I20" s="2">
         <v>7.6</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1338,13 +1338,13 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1405,13 +1405,13 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1787,25 +1787,25 @@
         <v>26</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>30.8</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J18">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1819,25 +1819,25 @@
         <v>26</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>30.8</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J19">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1845,28 +1845,28 @@
         <v>18</v>
       </c>
       <c r="D20">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J20">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>94.7</v>
       </c>
     </row>
   </sheetData>
@@ -2037,28 +2037,28 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>28</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H5" s="1">
-        <v>12.5</v>
+        <v>15.2</v>
       </c>
       <c r="I5" s="2">
         <v>7.6</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2104,28 +2104,28 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E7">
         <v>125</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1">
-        <v>74.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="I7" s="2">
         <v>6.9</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2486,16 +2486,16 @@
         <v>26</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>76.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="H18" s="1">
-        <v>23.1</v>
+        <v>30.8</v>
       </c>
       <c r="I18" s="2">
         <v>6.4</v>
@@ -2518,16 +2518,16 @@
         <v>26</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1">
-        <v>76.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="H19" s="1">
-        <v>23.1</v>
+        <v>30.8</v>
       </c>
       <c r="I19" s="2">
         <v>6.4</v>
@@ -2544,28 +2544,28 @@
         <v>18</v>
       </c>
       <c r="D20">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E20">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F20">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G20" s="1">
-        <v>84.8</v>
+        <v>84.2</v>
       </c>
       <c r="H20" s="1">
-        <v>15.2</v>
+        <v>15.8</v>
       </c>
       <c r="I20" s="2">
         <v>7.6</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -642,25 +642,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="I5" s="2">
         <v>7.6</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -709,25 +709,25 @@
         <v>168</v>
       </c>
       <c r="E7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
-        <v>74.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2">
         <v>6.9</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1149,25 +1149,25 @@
         <v>495</v>
       </c>
       <c r="E20">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F20">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20" s="1">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H20" s="1">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="I20" s="2">
         <v>7.6</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1236,25 +1236,25 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>38.7</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1271,25 +1271,25 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>73.2</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>26.8</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1306,25 +1306,25 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>23.3</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1341,25 +1341,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>78.8</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>21.2</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1376,25 +1376,25 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>18.2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1408,25 +1408,25 @@
         <v>168</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>25.6</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1443,25 +1443,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1478,25 +1478,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1513,25 +1513,25 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1548,25 +1548,25 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1583,25 +1583,25 @@
         <v>37</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>13.5</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1618,25 +1618,25 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>21.4</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1650,25 +1650,25 @@
         <v>235</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="F14">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>14.5</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1685,25 +1685,25 @@
         <v>34</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1720,25 +1720,25 @@
         <v>32</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1752,25 +1752,25 @@
         <v>66</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F17">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1848,25 +1848,25 @@
         <v>495</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>410</v>
       </c>
       <c r="F20">
-        <v>477</v>
+        <v>85</v>
       </c>
       <c r="G20" s="1">
-        <v>3.6</v>
+        <v>82.8</v>
       </c>
       <c r="H20" s="1">
-        <v>96.40000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="I20" s="2">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>94.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1935,19 +1935,19 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>64.5</v>
+        <v>61.3</v>
       </c>
       <c r="H2" s="1">
-        <v>35.5</v>
+        <v>38.7</v>
       </c>
       <c r="I2" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1970,19 +1970,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>53.7</v>
+        <v>73.2</v>
       </c>
       <c r="H3" s="1">
-        <v>46.3</v>
+        <v>26.8</v>
       </c>
       <c r="I3" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2005,19 +2005,19 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>83.3</v>
+        <v>76.7</v>
       </c>
       <c r="H4" s="1">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2040,25 +2040,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>84.8</v>
+        <v>78.8</v>
       </c>
       <c r="H5" s="1">
-        <v>15.2</v>
+        <v>21.2</v>
       </c>
       <c r="I5" s="2">
         <v>7.6</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2075,19 +2075,19 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H6" s="1">
-        <v>9.1</v>
+        <v>18.2</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2119,13 +2119,13 @@
         <v>25.6</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2154,7 +2154,7 @@
         <v>5.9</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2177,19 +2177,19 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>90.7</v>
+        <v>93</v>
       </c>
       <c r="H9" s="1">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2212,19 +2212,19 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>87.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>12.8</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2247,19 +2247,19 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>87.5</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2282,19 +2282,19 @@
         <v>37</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>89.2</v>
+        <v>86.5</v>
       </c>
       <c r="H12" s="1">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="I12" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2317,19 +2317,19 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>83.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>16.7</v>
+        <v>21.4</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2349,19 +2349,19 @@
         <v>235</v>
       </c>
       <c r="E14">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1">
-        <v>88.5</v>
+        <v>85.5</v>
       </c>
       <c r="H14" s="1">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2547,25 +2547,25 @@
         <v>495</v>
       </c>
       <c r="E20">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="F20">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G20" s="1">
-        <v>84.2</v>
+        <v>82.8</v>
       </c>
       <c r="H20" s="1">
-        <v>15.8</v>
+        <v>17.2</v>
       </c>
       <c r="I20" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -1180,8 +1180,7 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1879,8 +1878,7 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2396,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2431,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2463,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2486,19 +2484,19 @@
         <v>26</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="I18" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2518,19 +2516,19 @@
         <v>26</v>
       </c>
       <c r="E19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="I19" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2547,16 +2545,16 @@
         <v>495</v>
       </c>
       <c r="E20">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F20">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G20" s="1">
-        <v>82.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
       <c r="I20" s="2">
         <v>7.5</v>

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -1933,19 +1933,19 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>61.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>38.7</v>
+        <v>19.4</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2003,19 +2003,19 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>76.7</v>
+        <v>86.7</v>
       </c>
       <c r="H4" s="1">
-        <v>23.3</v>
+        <v>13.3</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>78.8</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2073,19 +2073,19 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>81.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>18.2</v>
+        <v>6.1</v>
       </c>
       <c r="I6" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2105,19 +2105,19 @@
         <v>168</v>
       </c>
       <c r="E7">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1">
-        <v>74.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="H7" s="1">
-        <v>25.6</v>
+        <v>13.7</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2545,19 +2545,19 @@
         <v>495</v>
       </c>
       <c r="E20">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="F20">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="G20" s="1">
-        <v>83.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="H20" s="1">
-        <v>16.4</v>
+        <v>12.3</v>
       </c>
       <c r="I20" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J20">
         <v>0</v>

--- a/academias/Química - Estadisticos 20222.xlsx
+++ b/academias/Química - Estadisticos 20222.xlsx
@@ -1968,19 +1968,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>73.2</v>
+        <v>92.7</v>
       </c>
       <c r="H3" s="1">
-        <v>26.8</v>
+        <v>7.3</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2105,16 +2105,16 @@
         <v>168</v>
       </c>
       <c r="E7">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>86.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>13.7</v>
+        <v>8.9</v>
       </c>
       <c r="I7" s="2">
         <v>7.3</v>
@@ -2140,19 +2140,19 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>94.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="H8" s="1">
-        <v>5.9</v>
+        <v>14.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2175,19 +2175,19 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>93</v>
+        <v>97.7</v>
       </c>
       <c r="H9" s="1">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2210,19 +2210,19 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>25.6</v>
+      </c>
+      <c r="I10" s="2">
         <v>7</v>
-      </c>
-      <c r="G10" s="1">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="H10" s="1">
-        <v>17.9</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2245,19 +2245,19 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H11" s="1">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2280,19 +2280,19 @@
         <v>37</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>86.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>13.5</v>
+        <v>18.9</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>78.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="H13" s="1">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2347,19 +2347,19 @@
         <v>235</v>
       </c>
       <c r="E14">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1">
-        <v>85.5</v>
+        <v>83</v>
       </c>
       <c r="H14" s="1">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="I14" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2545,19 +2545,19 @@
         <v>495</v>
       </c>
       <c r="E20">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F20">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G20" s="1">
-        <v>87.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="I20" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J20">
         <v>0</v>
